--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8255,0.0607,0.0139,0.0831</t>
-  </si>
-  <si>
-    <t>0.0276,0.0023,0.0030,0.9849</t>
-  </si>
-  <si>
-    <t>0.5911,0.0160,0.0147,0.4428</t>
-  </si>
-  <si>
-    <t>0.0398,0.0064,0.0047,0.9796</t>
-  </si>
-  <si>
-    <t>0.9948,0.0017,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9944,0.0023,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9911,0.0034,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9947,0.0011,0.0003,0.0012</t>
-  </si>
-  <si>
-    <t>0.9898,0.0076,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9920,0.0054,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0013,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9972,0.0006,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.7217,0.1410,0.1947,0.0125</t>
-  </si>
-  <si>
-    <t>0.5601,0.0205,0.5284,0.0065</t>
-  </si>
-  <si>
-    <t>0.6749,0.0321,0.3678,0.0007</t>
-  </si>
-  <si>
-    <t>0.3748,0.0435,0.6488,0.0064</t>
-  </si>
-  <si>
-    <t>0.6912,0.0109,0.3767,0.0056</t>
-  </si>
-  <si>
-    <t>0.0011,0.9956,0.0019,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.9967,0.0028,0.0006</t>
-  </si>
-  <si>
-    <t>0.0770,0.9322,0.0058,0.0005</t>
-  </si>
-  <si>
-    <t>0.0061,0.9881,0.0051,0.0005</t>
-  </si>
-  <si>
-    <t>0.0016,0.9947,0.0016,0.0003</t>
-  </si>
-  <si>
-    <t>0.8279,0.0052,0.1803,0.0036</t>
-  </si>
-  <si>
-    <t>0.2826,0.0337,0.7363,0.0181</t>
-  </si>
-  <si>
-    <t>0.0168,0.0042,0.9799,0.0049</t>
-  </si>
-  <si>
-    <t>0.1978,0.0155,0.8505,0.0035</t>
-  </si>
-  <si>
-    <t>0.0052,0.0025,0.9900,0.0017</t>
-  </si>
-  <si>
-    <t>0.0383,0.0112,0.8774,0.1164</t>
-  </si>
-  <si>
-    <t>0.0039,0.0023,0.9875,0.0116</t>
-  </si>
-  <si>
-    <t>0.2415,0.7903,0.0081,0.0042</t>
-  </si>
-  <si>
-    <t>0.3515,0.1277,0.5611,0.0065</t>
-  </si>
-  <si>
-    <t>0.0026,0.0087,0.9900,0.0088</t>
-  </si>
-  <si>
-    <t>0.0103,0.9399,0.1991,0.0006</t>
-  </si>
-  <si>
-    <t>0.8516,0.0931,0.0336,0.0192</t>
-  </si>
-  <si>
-    <t>0.0699,0.0286,0.9389,0.0024</t>
-  </si>
-  <si>
-    <t>0.7303,0.3952,0.0045,0.0005</t>
-  </si>
-  <si>
-    <t>0.0337,0.9388,0.0724,0.0021</t>
-  </si>
-  <si>
-    <t>0.0144,0.7283,0.7936,0.0103</t>
-  </si>
-  <si>
-    <t>0.0703,0.1755,0.8835,0.0041</t>
-  </si>
-  <si>
-    <t>0.0670,0.0146,0.9252,0.0056</t>
-  </si>
-  <si>
-    <t>0.0396,0.0095,0.9240,0.0475</t>
-  </si>
-  <si>
-    <t>0.0431,0.3684,0.8645,0.0043</t>
-  </si>
-  <si>
-    <t>0.0102,0.9646,0.0747,0.0031</t>
-  </si>
-  <si>
-    <t>0.0541,0.1187,0.9010,0.0031</t>
-  </si>
-  <si>
-    <t>0.0447,0.6086,0.0114,0.8224</t>
-  </si>
-  <si>
-    <t>0.0036,0.9710,0.0108,0.0205</t>
-  </si>
-  <si>
-    <t>0.0033,0.9901,0.0127,0.0002</t>
-  </si>
-  <si>
-    <t>0.0084,0.9777,0.0347,0.0006</t>
-  </si>
-  <si>
-    <t>0.0015,0.0330,0.9833,0.0052</t>
-  </si>
-  <si>
-    <t>0.0038,0.0654,0.9881,0.0001</t>
-  </si>
-  <si>
-    <t>0.0320,0.0029,0.9489,0.0194</t>
-  </si>
-  <si>
-    <t>0.0225,0.0030,0.9739,0.0045</t>
-  </si>
-  <si>
-    <t>0.0136,0.0415,0.9639,0.0130</t>
-  </si>
-  <si>
-    <t>0.0147,0.0074,0.9800,0.0015</t>
-  </si>
-  <si>
-    <t>0.9866,0.0095,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9704,0.0233,0.0027,0.0023</t>
-  </si>
-  <si>
-    <t>0.9800,0.0070,0.0023,0.0036</t>
-  </si>
-  <si>
-    <t>0.0009,0.0137,0.9927,0.0067</t>
-  </si>
-  <si>
-    <t>0.9864,0.0064,0.0023,0.0020</t>
-  </si>
-  <si>
-    <t>0.9939,0.0030,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9653,0.0281,0.0015,0.0025</t>
-  </si>
-  <si>
-    <t>0.0044,0.7764,0.8903,0.0014</t>
-  </si>
-  <si>
-    <t>0.0200,0.0142,0.9762,0.0037</t>
-  </si>
-  <si>
-    <t>0.0020,0.0087,0.9800,0.0149</t>
-  </si>
-  <si>
-    <t>0.0013,0.7244,0.9717,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0018,0.9980,0.0008</t>
-  </si>
-  <si>
-    <t>0.0461,0.9208,0.0673,0.0019</t>
-  </si>
-  <si>
-    <t>0.0084,0.9874,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.8203,0.0173,0.2022,0.0057</t>
-  </si>
-  <si>
-    <t>0.8331,0.1687,0.0364,0.0050</t>
-  </si>
-  <si>
-    <t>0.0013,0.0132,0.9957,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.3117,0.9924,0.0001</t>
-  </si>
-  <si>
-    <t>0.0079,0.5621,0.8896,0.0006</t>
-  </si>
-  <si>
-    <t>0.0011,0.9792,0.2575,0.0012</t>
-  </si>
-  <si>
-    <t>0.0002,0.9773,0.9136,0.0000</t>
-  </si>
-  <si>
-    <t>0.0954,0.0010,0.0177,0.8996</t>
-  </si>
-  <si>
-    <t>0.0006,0.0020,0.0003,0.9993</t>
-  </si>
-  <si>
-    <t>0.0007,0.0031,0.0019,0.9984</t>
-  </si>
-  <si>
-    <t>0.0390,0.0050,0.0057,0.9759</t>
-  </si>
-  <si>
-    <t>0.0070,0.0057,0.0068,0.9915</t>
-  </si>
-  <si>
-    <t>0.0010,0.0010,0.0035,0.9978</t>
-  </si>
-  <si>
-    <t>0.0028,0.8084,0.9169,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.8595,0.9719,0.0000</t>
-  </si>
-  <si>
-    <t>0.0080,0.8549,0.6498,0.0009</t>
-  </si>
-  <si>
-    <t>0.0015,0.2121,0.9856,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9822,0.9033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0082,0.4985,0.9164,0.0018</t>
-  </si>
-  <si>
-    <t>0.9917,0.0058,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9833,0.0109,0.0006,0.0019</t>
-  </si>
-  <si>
-    <t>0.9883,0.0094,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.9886,0.0052,0.0007,0.0016</t>
-  </si>
-  <si>
-    <t>0.9859,0.0131,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9749,0.0319,0.0036,0.0008</t>
-  </si>
-  <si>
-    <t>0.9826,0.0154,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.9751,0.0174,0.0031,0.0021</t>
-  </si>
-  <si>
-    <t>0.9944,0.0032,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9922,0.0041,0.0009,0.0012</t>
-  </si>
-  <si>
-    <t>0.9950,0.0017,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9974,0.0009,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0096,0.0013,0.0029</t>
-  </si>
-  <si>
-    <t>0.9873,0.0080,0.0011,0.0016</t>
-  </si>
-  <si>
-    <t>0.9959,0.0015,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9945,0.0023,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.0113,0.0013,0.9852,0.0038</t>
-  </si>
-  <si>
-    <t>0.0188,0.0103,0.9746,0.0011</t>
-  </si>
-  <si>
-    <t>0.8754,0.0066,0.0735,0.0136</t>
-  </si>
-  <si>
-    <t>0.2356,0.0025,0.8423,0.0038</t>
-  </si>
-  <si>
-    <t>0.1020,0.9130,0.0050,0.0011</t>
-  </si>
-  <si>
-    <t>0.0201,0.9760,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.0222,0.9709,0.0024,0.0018</t>
-  </si>
-  <si>
-    <t>0.3742,0.7281,0.0094,0.0017</t>
-  </si>
-  <si>
-    <t>0.0117,0.9729,0.0103,0.0022</t>
-  </si>
-  <si>
-    <t>0.0040,0.9933,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.8391,0.2160,0.0181,0.0013</t>
-  </si>
-  <si>
-    <t>0.7370,0.2103,0.0879,0.0198</t>
-  </si>
-  <si>
-    <t>0.3988,0.0110,0.7183,0.0042</t>
-  </si>
-  <si>
-    <t>0.5945,0.0644,0.3964,0.0074</t>
-  </si>
-  <si>
-    <t>0.2446,0.0541,0.7248,0.0076</t>
-  </si>
-  <si>
-    <t>0.0742,0.2639,0.0283,0.9125</t>
-  </si>
-  <si>
-    <t>0.0017,0.9908,0.0040,0.0021</t>
-  </si>
-  <si>
-    <t>0.0006,0.9927,0.0018,0.0090</t>
-  </si>
-  <si>
-    <t>0.0100,0.9640,0.0089,0.0689</t>
-  </si>
-  <si>
-    <t>0.0012,0.9760,0.5937,0.0005</t>
-  </si>
-  <si>
-    <t>0.0206,0.9673,0.0365,0.0008</t>
-  </si>
-  <si>
-    <t>0.6814,0.3686,0.0315,0.0032</t>
-  </si>
-  <si>
-    <t>0.8035,0.2196,0.0297,0.0032</t>
-  </si>
-  <si>
-    <t>0.9741,0.0297,0.0033,0.0008</t>
-  </si>
-  <si>
-    <t>0.9892,0.0015,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9762,0.0082,0.0035,0.0064</t>
-  </si>
-  <si>
-    <t>0.9559,0.0179,0.0111,0.0062</t>
-  </si>
-  <si>
-    <t>0.9874,0.0017,0.0011,0.0057</t>
-  </si>
-  <si>
-    <t>0.9908,0.0055,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9818,0.0053,0.0026,0.0036</t>
-  </si>
-  <si>
-    <t>0.9905,0.0012,0.0006,0.0025</t>
-  </si>
-  <si>
-    <t>0.0030,0.7276,0.8795,0.0008</t>
-  </si>
-  <si>
-    <t>0.0041,0.8292,0.7460,0.0003</t>
-  </si>
-  <si>
-    <t>0.0051,0.2765,0.9440,0.0006</t>
-  </si>
-  <si>
-    <t>0.0301,0.0378,0.9468,0.0041</t>
-  </si>
-  <si>
-    <t>0.7949,0.0417,0.1391,0.0214</t>
-  </si>
-  <si>
-    <t>0.7149,0.2142,0.0196,0.0464</t>
-  </si>
-  <si>
-    <t>0.2852,0.0071,0.7780,0.0109</t>
-  </si>
-  <si>
-    <t>0.5132,0.0574,0.4976,0.0120</t>
-  </si>
-  <si>
-    <t>0.0240,0.0031,0.0027,0.9866</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0041,0.9992</t>
-  </si>
-  <si>
-    <t>0.0014,0.0010,0.0011,0.9982</t>
-  </si>
-  <si>
-    <t>0.0542,0.0011,0.0090,0.9570</t>
-  </si>
-  <si>
-    <t>0.0006,0.8609,0.9367,0.0003</t>
-  </si>
-  <si>
-    <t>0.9522,0.0679,0.0028,0.0014</t>
-  </si>
-  <si>
-    <t>0.2910,0.7322,0.0134,0.0067</t>
-  </si>
-  <si>
-    <t>0.9744,0.0109,0.0010,0.0063</t>
-  </si>
-  <si>
-    <t>0.8781,0.1793,0.0056,0.0018</t>
-  </si>
-  <si>
-    <t>0.9729,0.0074,0.0059,0.0055</t>
-  </si>
-  <si>
-    <t>0.2088,0.0116,0.0221,0.8572</t>
-  </si>
-  <si>
-    <t>0.9579,0.0304,0.0060,0.0029</t>
-  </si>
-  <si>
-    <t>0.0006,0.0957,0.9733,0.0058</t>
-  </si>
-  <si>
-    <t>0.8927,0.0018,0.0047,0.0983</t>
-  </si>
-  <si>
-    <t>0.7538,0.0058,0.0503,0.1483</t>
-  </si>
-  <si>
-    <t>0.2865,0.7467,0.0335,0.0063</t>
-  </si>
-  <si>
-    <t>0.9418,0.0385,0.0030,0.0051</t>
-  </si>
-  <si>
-    <t>0.9543,0.0174,0.0189,0.0028</t>
-  </si>
-  <si>
-    <t>0.3813,0.5631,0.1370,0.0439</t>
-  </si>
-  <si>
-    <t>0.8912,0.0862,0.0285,0.0030</t>
-  </si>
-  <si>
-    <t>0.8901,0.0771,0.0390,0.0019</t>
-  </si>
-  <si>
-    <t>0.9880,0.0036,0.0012,0.0023</t>
-  </si>
-  <si>
-    <t>0.9805,0.0139,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9866,0.0060,0.0022,0.0013</t>
-  </si>
-  <si>
-    <t>0.9826,0.0010,0.0011,0.0105</t>
-  </si>
-  <si>
-    <t>0.9773,0.0080,0.0039,0.0030</t>
-  </si>
-  <si>
-    <t>0.9677,0.0130,0.0044,0.0067</t>
-  </si>
-  <si>
-    <t>0.9878,0.0041,0.0005,0.0024</t>
-  </si>
-  <si>
-    <t>0.9828,0.0047,0.0029,0.0035</t>
-  </si>
-  <si>
-    <t>0.7999,0.2395,0.0245,0.0091</t>
-  </si>
-  <si>
-    <t>0.2282,0.8402,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.4173,0.7101,0.0025,0.0010</t>
-  </si>
-  <si>
-    <t>0.5442,0.3981,0.1275,0.0196</t>
-  </si>
-  <si>
-    <t>0.9681,0.0512,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.9197,0.0670,0.0128,0.0123</t>
-  </si>
-  <si>
-    <t>0.8323,0.1937,0.0060,0.0132</t>
-  </si>
-  <si>
-    <t>0.4552,0.6522,0.0051,0.0017</t>
-  </si>
-  <si>
-    <t>0.0104,0.0100,0.9918,0.0003</t>
-  </si>
-  <si>
-    <t>0.8823,0.1238,0.0212,0.0023</t>
-  </si>
-  <si>
-    <t>0.0069,0.0043,0.9897,0.0011</t>
-  </si>
-  <si>
-    <t>0.0028,0.0060,0.9711,0.0445</t>
-  </si>
-  <si>
-    <t>0.0178,0.0045,0.9694,0.0148</t>
-  </si>
-  <si>
-    <t>0.0082,0.1216,0.9688,0.0010</t>
-  </si>
-  <si>
-    <t>0.0179,0.0092,0.9822,0.0005</t>
-  </si>
-  <si>
-    <t>0.0186,0.0017,0.9864,0.0009</t>
-  </si>
-  <si>
-    <t>0.0150,0.0026,0.9833,0.0027</t>
-  </si>
-  <si>
-    <t>0.0884,0.0187,0.9099,0.0082</t>
-  </si>
-  <si>
-    <t>0.1717,0.0208,0.8679,0.0029</t>
-  </si>
-  <si>
-    <t>0.2509,0.3693,0.4123,0.0167</t>
-  </si>
-  <si>
-    <t>0.3345,0.1076,0.5144,0.0047</t>
-  </si>
-  <si>
-    <t>0.6087,0.0387,0.4304,0.0049</t>
-  </si>
-  <si>
-    <t>0.5174,0.0313,0.4517,0.0015</t>
-  </si>
-  <si>
-    <t>0.8377,0.0380,0.1096,0.0139</t>
-  </si>
-  <si>
-    <t>0.4334,0.0428,0.5825,0.0213</t>
-  </si>
-  <si>
-    <t>0.7058,0.3377,0.0254,0.0028</t>
-  </si>
-  <si>
-    <t>0.0532,0.9521,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.3358,0.7602,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9511,0.0856,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.6377,0.4962,0.0073,0.0031</t>
-  </si>
-  <si>
-    <t>0.6778,0.0977,0.1809,0.1341</t>
-  </si>
-  <si>
-    <t>0.8151,0.0086,0.1659,0.0102</t>
-  </si>
-  <si>
-    <t>0.9060,0.0097,0.0214,0.0243</t>
-  </si>
-  <si>
-    <t>0.4841,0.0260,0.5656,0.0172</t>
-  </si>
-  <si>
-    <t>0.2978,0.0100,0.6754,0.0366</t>
-  </si>
-  <si>
-    <t>0.1629,0.0238,0.8540,0.0201</t>
-  </si>
-  <si>
-    <t>0.0074,0.2295,0.9293,0.0047</t>
-  </si>
-  <si>
-    <t>0.0235,0.2633,0.9300,0.0065</t>
-  </si>
-  <si>
-    <t>0.0040,0.0125,0.9870,0.0048</t>
-  </si>
-  <si>
-    <t>0.0488,0.1543,0.8467,0.0062</t>
-  </si>
-  <si>
-    <t>0.9893,0.0039,0.0013,0.0019</t>
-  </si>
-  <si>
-    <t>0.9321,0.0777,0.0089,0.0030</t>
-  </si>
-  <si>
-    <t>0.9708,0.0132,0.0036,0.0048</t>
-  </si>
-  <si>
-    <t>0.9877,0.0110,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9852,0.0091,0.0017,0.0017</t>
-  </si>
-  <si>
-    <t>0.9916,0.0046,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9933,0.0029,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9859,0.0091,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.0218,0.0049,0.9736,0.0026</t>
-  </si>
-  <si>
-    <t>0.4173,0.3016,0.4578,0.0794</t>
-  </si>
-  <si>
-    <t>0.8939,0.0253,0.0759,0.0079</t>
-  </si>
-  <si>
-    <t>0.0074,0.0110,0.9885,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.0029,0.9942,0.0116</t>
-  </si>
-  <si>
-    <t>0.0350,0.0303,0.9390,0.0025</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.9979,0.0020</t>
-  </si>
-  <si>
-    <t>0.1308,0.0190,0.8649,0.0108</t>
-  </si>
-  <si>
-    <t>0.0024,0.0171,0.9907,0.0031</t>
-  </si>
-  <si>
-    <t>0.0054,0.0066,0.9836,0.0070</t>
-  </si>
-  <si>
-    <t>0.0628,0.1119,0.8627,0.0059</t>
-  </si>
-  <si>
-    <t>0.7850,0.0028,0.2332,0.0051</t>
-  </si>
-  <si>
-    <t>0.6344,0.0105,0.4228,0.0091</t>
-  </si>
-  <si>
-    <t>0.8101,0.0332,0.1415,0.0166</t>
-  </si>
-  <si>
-    <t>0.9723,0.0323,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9812,0.0114,0.0020,0.0022</t>
-  </si>
-  <si>
-    <t>0.9911,0.0074,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9823,0.0097,0.0024,0.0023</t>
-  </si>
-  <si>
-    <t>0.9914,0.0025,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9937,0.0037,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.9922,0.0036,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9907,0.0026,0.0006,0.0024</t>
-  </si>
-  <si>
-    <t>0.0355,0.2398,0.7766,0.0074</t>
-  </si>
-  <si>
-    <t>0.0038,0.0245,0.9925,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.0039,0.9893,0.0013</t>
-  </si>
-  <si>
-    <t>0.1499,0.0075,0.8833,0.0020</t>
-  </si>
-  <si>
-    <t>0.0426,0.0033,0.9692,0.0018</t>
-  </si>
-  <si>
-    <t>0.1845,0.0065,0.6392,0.1408</t>
-  </si>
-  <si>
-    <t>0.2017,0.0211,0.7641,0.0524</t>
-  </si>
-  <si>
-    <t>0.0012,0.0081,0.9865,0.0195</t>
-  </si>
-  <si>
-    <t>0.6422,0.0008,0.0027,0.5299</t>
-  </si>
-  <si>
-    <t>0.0282,0.0810,0.0032,0.9738</t>
-  </si>
-  <si>
-    <t>0.0641,0.0103,0.0009,0.9758</t>
-  </si>
-  <si>
-    <t>0.0021,0.0003,0.0012,0.9981</t>
-  </si>
-  <si>
-    <t>0.0025,0.0002,0.0009,0.9980</t>
-  </si>
-  <si>
-    <t>0.8988,0.0153,0.0312,0.0280</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7094,0.1850,0.1011,0.0559</t>
+  </si>
+  <si>
+    <t>0.0051,0.0012,0.0034,0.9955</t>
+  </si>
+  <si>
+    <t>0.4595,0.0358,0.0161,0.5713</t>
+  </si>
+  <si>
+    <t>0.0710,0.0209,0.0051,0.9636</t>
+  </si>
+  <si>
+    <t>0.9951,0.0019,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0033,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9868,0.0076,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9934,0.0010,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9825,0.0283,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9882,0.0103,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9946,0.0017,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.5127,0.3960,0.1863,0.0191</t>
+  </si>
+  <si>
+    <t>0.1707,0.0138,0.8855,0.0034</t>
+  </si>
+  <si>
+    <t>0.1810,0.1539,0.6611,0.0051</t>
+  </si>
+  <si>
+    <t>0.2039,0.0596,0.7617,0.0327</t>
+  </si>
+  <si>
+    <t>0.5960,0.0125,0.4837,0.0110</t>
+  </si>
+  <si>
+    <t>0.0109,0.9836,0.0048,0.0005</t>
+  </si>
+  <si>
+    <t>0.0053,0.9909,0.0034,0.0002</t>
+  </si>
+  <si>
+    <t>0.0210,0.9672,0.0211,0.0012</t>
+  </si>
+  <si>
+    <t>0.0555,0.9625,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.9960,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.6963,0.0330,0.2480,0.0506</t>
+  </si>
+  <si>
+    <t>0.6317,0.0113,0.3922,0.0079</t>
+  </si>
+  <si>
+    <t>0.0216,0.0066,0.9733,0.0041</t>
+  </si>
+  <si>
+    <t>0.0693,0.0175,0.8967,0.0261</t>
+  </si>
+  <si>
+    <t>0.0082,0.0017,0.9861,0.0026</t>
+  </si>
+  <si>
+    <t>0.0151,0.0102,0.9651,0.0171</t>
+  </si>
+  <si>
+    <t>0.0014,0.0008,0.9896,0.0233</t>
+  </si>
+  <si>
+    <t>0.5780,0.4899,0.0267,0.0038</t>
+  </si>
+  <si>
+    <t>0.5901,0.1440,0.3496,0.0120</t>
+  </si>
+  <si>
+    <t>0.0009,0.0205,0.9874,0.0131</t>
+  </si>
+  <si>
+    <t>0.0043,0.8864,0.3898,0.0002</t>
+  </si>
+  <si>
+    <t>0.8078,0.1318,0.1009,0.0109</t>
+  </si>
+  <si>
+    <t>0.2781,0.0339,0.7992,0.0034</t>
+  </si>
+  <si>
+    <t>0.7308,0.3427,0.0179,0.0030</t>
+  </si>
+  <si>
+    <t>0.0201,0.9311,0.1988,0.0040</t>
+  </si>
+  <si>
+    <t>0.0739,0.6106,0.3810,0.0338</t>
+  </si>
+  <si>
+    <t>0.0068,0.4883,0.9593,0.0006</t>
+  </si>
+  <si>
+    <t>0.0529,0.2334,0.8976,0.0083</t>
+  </si>
+  <si>
+    <t>0.0250,0.0068,0.9576,0.0125</t>
+  </si>
+  <si>
+    <t>0.0073,0.0274,0.9833,0.0031</t>
+  </si>
+  <si>
+    <t>0.0036,0.9757,0.1068,0.0014</t>
+  </si>
+  <si>
+    <t>0.0088,0.0511,0.9754,0.0037</t>
+  </si>
+  <si>
+    <t>0.4040,0.4086,0.0278,0.3283</t>
+  </si>
+  <si>
+    <t>0.0010,0.9712,0.0010,0.1085</t>
+  </si>
+  <si>
+    <t>0.0087,0.9555,0.1151,0.0016</t>
+  </si>
+  <si>
+    <t>0.0029,0.9866,0.0047,0.0019</t>
+  </si>
+  <si>
+    <t>0.0051,0.2763,0.9306,0.0073</t>
+  </si>
+  <si>
+    <t>0.0119,0.0275,0.9787,0.0025</t>
+  </si>
+  <si>
+    <t>0.1002,0.0026,0.9294,0.0042</t>
+  </si>
+  <si>
+    <t>0.0086,0.0021,0.9809,0.0053</t>
+  </si>
+  <si>
+    <t>0.0036,0.0139,0.9761,0.0145</t>
+  </si>
+  <si>
+    <t>0.0060,0.0129,0.9867,0.0024</t>
+  </si>
+  <si>
+    <t>0.9457,0.0535,0.0102,0.0037</t>
+  </si>
+  <si>
+    <t>0.9767,0.0087,0.0057,0.0028</t>
+  </si>
+  <si>
+    <t>0.9816,0.0091,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.0059,0.0262,0.9868,0.0029</t>
+  </si>
+  <si>
+    <t>0.9845,0.0060,0.0016,0.0033</t>
+  </si>
+  <si>
+    <t>0.9519,0.0221,0.0211,0.0071</t>
+  </si>
+  <si>
+    <t>0.9528,0.0539,0.0042,0.0025</t>
+  </si>
+  <si>
+    <t>0.0164,0.5889,0.8609,0.0117</t>
+  </si>
+  <si>
+    <t>0.0219,0.2458,0.9295,0.0034</t>
+  </si>
+  <si>
+    <t>0.0015,0.0208,0.9850,0.0056</t>
+  </si>
+  <si>
+    <t>0.0001,0.9490,0.9784,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0100,0.9956,0.0009</t>
+  </si>
+  <si>
+    <t>0.0047,0.9711,0.1569,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9978,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.8997,0.0600,0.0414,0.0077</t>
+  </si>
+  <si>
+    <t>0.3470,0.1383,0.5233,0.0030</t>
+  </si>
+  <si>
+    <t>0.0234,0.0343,0.9646,0.0015</t>
+  </si>
+  <si>
+    <t>0.0033,0.8982,0.7827,0.0015</t>
+  </si>
+  <si>
+    <t>0.0335,0.5459,0.6218,0.0015</t>
+  </si>
+  <si>
+    <t>0.0007,0.9895,0.0511,0.0029</t>
+  </si>
+  <si>
+    <t>0.0006,0.9458,0.9306,0.0001</t>
+  </si>
+  <si>
+    <t>0.0904,0.0011,0.0692,0.7829</t>
+  </si>
+  <si>
+    <t>0.0002,0.0046,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0028,0.0006,0.0032,0.9956</t>
+  </si>
+  <si>
+    <t>0.0156,0.0166,0.0012,0.9913</t>
+  </si>
+  <si>
+    <t>0.0341,0.0017,0.0052,0.9802</t>
+  </si>
+  <si>
+    <t>0.0040,0.0017,0.0004,0.9979</t>
+  </si>
+  <si>
+    <t>0.0010,0.9651,0.7579,0.0001</t>
+  </si>
+  <si>
+    <t>0.0047,0.4455,0.9623,0.0002</t>
+  </si>
+  <si>
+    <t>0.0031,0.6127,0.8744,0.0016</t>
+  </si>
+  <si>
+    <t>0.0012,0.6375,0.9573,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9645,0.9332,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9369,0.7705,0.0002</t>
+  </si>
+  <si>
+    <t>0.9913,0.0036,0.0012,0.0014</t>
+  </si>
+  <si>
+    <t>0.9866,0.0074,0.0013,0.0019</t>
+  </si>
+  <si>
+    <t>0.9843,0.0152,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.9843,0.0131,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9817,0.0082,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9873,0.0017,0.0006,0.0055</t>
+  </si>
+  <si>
+    <t>0.9754,0.0183,0.0016,0.0032</t>
+  </si>
+  <si>
+    <t>0.9857,0.0046,0.0012,0.0030</t>
+  </si>
+  <si>
+    <t>0.9926,0.0046,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9947,0.0021,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9875,0.0011,0.0002,0.0051</t>
+  </si>
+  <si>
+    <t>0.9953,0.0015,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9929,0.0045,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9931,0.0035,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9936,0.0026,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9882,0.0053,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.0012,0.0007,0.9945,0.0042</t>
+  </si>
+  <si>
+    <t>0.0810,0.0551,0.8698,0.0031</t>
+  </si>
+  <si>
+    <t>0.6058,0.0037,0.2767,0.0354</t>
+  </si>
+  <si>
+    <t>0.1061,0.0095,0.9145,0.0099</t>
+  </si>
+  <si>
+    <t>0.0378,0.9530,0.0044,0.0015</t>
+  </si>
+  <si>
+    <t>0.0049,0.9880,0.0022,0.0016</t>
+  </si>
+  <si>
+    <t>0.0206,0.9705,0.0014,0.0022</t>
+  </si>
+  <si>
+    <t>0.2571,0.8120,0.0047,0.0027</t>
+  </si>
+  <si>
+    <t>0.0456,0.9476,0.0055,0.0020</t>
+  </si>
+  <si>
+    <t>0.0053,0.9905,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.6760,0.3550,0.0314,0.0052</t>
+  </si>
+  <si>
+    <t>0.4442,0.5133,0.2129,0.0427</t>
+  </si>
+  <si>
+    <t>0.2257,0.0158,0.8276,0.0058</t>
+  </si>
+  <si>
+    <t>0.6253,0.0780,0.0425,0.2229</t>
+  </si>
+  <si>
+    <t>0.5515,0.0073,0.5591,0.0035</t>
+  </si>
+  <si>
+    <t>0.1022,0.2943,0.0765,0.8622</t>
+  </si>
+  <si>
+    <t>0.0022,0.9849,0.0306,0.0043</t>
+  </si>
+  <si>
+    <t>0.0040,0.9624,0.0043,0.0283</t>
+  </si>
+  <si>
+    <t>0.1212,0.8004,0.1019,0.0859</t>
+  </si>
+  <si>
+    <t>0.0001,0.9023,0.9841,0.0000</t>
+  </si>
+  <si>
+    <t>0.0266,0.9593,0.0507,0.0006</t>
+  </si>
+  <si>
+    <t>0.6997,0.3376,0.0387,0.0030</t>
+  </si>
+  <si>
+    <t>0.5542,0.4550,0.0839,0.0059</t>
+  </si>
+  <si>
+    <t>0.9852,0.0049,0.0026,0.0031</t>
+  </si>
+  <si>
+    <t>0.9877,0.0032,0.0012,0.0025</t>
+  </si>
+  <si>
+    <t>0.9915,0.0047,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9878,0.0041,0.0013,0.0021</t>
+  </si>
+  <si>
+    <t>0.9918,0.0012,0.0011,0.0027</t>
+  </si>
+  <si>
+    <t>0.9637,0.0201,0.0111,0.0033</t>
+  </si>
+  <si>
+    <t>0.9909,0.0026,0.0005,0.0022</t>
+  </si>
+  <si>
+    <t>0.9449,0.0069,0.0120,0.0216</t>
+  </si>
+  <si>
+    <t>0.0013,0.9284,0.8030,0.0003</t>
+  </si>
+  <si>
+    <t>0.0402,0.1346,0.8293,0.0003</t>
+  </si>
+  <si>
+    <t>0.0084,0.2280,0.9475,0.0011</t>
+  </si>
+  <si>
+    <t>0.0783,0.0465,0.9022,0.0007</t>
+  </si>
+  <si>
+    <t>0.8316,0.0869,0.0394,0.0450</t>
+  </si>
+  <si>
+    <t>0.7964,0.0205,0.1627,0.0268</t>
+  </si>
+  <si>
+    <t>0.4236,0.0015,0.6703,0.0059</t>
+  </si>
+  <si>
+    <t>0.4110,0.4891,0.1931,0.0317</t>
+  </si>
+  <si>
+    <t>0.1216,0.0025,0.0011,0.9635</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0041,0.9993</t>
+  </si>
+  <si>
+    <t>0.0010,0.0049,0.0008,0.9985</t>
+  </si>
+  <si>
+    <t>0.0009,0.0011,0.0033,0.9982</t>
+  </si>
+  <si>
+    <t>0.0007,0.8521,0.9602,0.0001</t>
+  </si>
+  <si>
+    <t>0.9413,0.0525,0.0070,0.0051</t>
+  </si>
+  <si>
+    <t>0.0326,0.9521,0.0052,0.0039</t>
+  </si>
+  <si>
+    <t>0.9723,0.0078,0.0033,0.0111</t>
+  </si>
+  <si>
+    <t>0.7148,0.4058,0.0044,0.0012</t>
+  </si>
+  <si>
+    <t>0.9779,0.0031,0.0028,0.0095</t>
+  </si>
+  <si>
+    <t>0.1869,0.0084,0.0025,0.9025</t>
+  </si>
+  <si>
+    <t>0.9639,0.0019,0.0005,0.0261</t>
+  </si>
+  <si>
+    <t>0.0005,0.0301,0.9912,0.0029</t>
+  </si>
+  <si>
+    <t>0.8698,0.0048,0.0103,0.1221</t>
+  </si>
+  <si>
+    <t>0.9210,0.0061,0.0049,0.0447</t>
+  </si>
+  <si>
+    <t>0.7065,0.2880,0.0772,0.0087</t>
+  </si>
+  <si>
+    <t>0.8904,0.0262,0.0201,0.0402</t>
+  </si>
+  <si>
+    <t>0.9185,0.0587,0.0244,0.0033</t>
+  </si>
+  <si>
+    <t>0.5051,0.2951,0.3075,0.0365</t>
+  </si>
+  <si>
+    <t>0.6063,0.4246,0.0489,0.0034</t>
+  </si>
+  <si>
+    <t>0.8795,0.1322,0.0216,0.0016</t>
+  </si>
+  <si>
+    <t>0.9930,0.0016,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.9833,0.0050,0.0007,0.0027</t>
+  </si>
+  <si>
+    <t>0.9925,0.0017,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9948,0.0007,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.9815,0.0021,0.0008,0.0070</t>
+  </si>
+  <si>
+    <t>0.9095,0.1042,0.0076,0.0059</t>
+  </si>
+  <si>
+    <t>0.9873,0.0057,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.9871,0.0044,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.7116,0.4177,0.0048,0.0015</t>
+  </si>
+  <si>
+    <t>0.8792,0.1655,0.0087,0.0013</t>
+  </si>
+  <si>
+    <t>0.4029,0.6463,0.0197,0.0051</t>
+  </si>
+  <si>
+    <t>0.0426,0.1182,0.9394,0.0024</t>
+  </si>
+  <si>
+    <t>0.9536,0.0475,0.0036,0.0027</t>
+  </si>
+  <si>
+    <t>0.9218,0.0749,0.0155,0.0064</t>
+  </si>
+  <si>
+    <t>0.6918,0.4253,0.0091,0.0027</t>
+  </si>
+  <si>
+    <t>0.8769,0.1357,0.0239,0.0024</t>
+  </si>
+  <si>
+    <t>0.0036,0.0209,0.9929,0.0009</t>
+  </si>
+  <si>
+    <t>0.8977,0.0829,0.0347,0.0024</t>
+  </si>
+  <si>
+    <t>0.0007,0.0014,0.9966,0.0025</t>
+  </si>
+  <si>
+    <t>0.0110,0.0668,0.9459,0.0317</t>
+  </si>
+  <si>
+    <t>0.2946,0.0041,0.7744,0.0077</t>
+  </si>
+  <si>
+    <t>0.0048,0.1129,0.9835,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.0122,0.9866,0.0023</t>
+  </si>
+  <si>
+    <t>0.0031,0.0007,0.9951,0.0007</t>
+  </si>
+  <si>
+    <t>0.0033,0.0060,0.9909,0.0010</t>
+  </si>
+  <si>
+    <t>0.4284,0.1063,0.5371,0.0247</t>
+  </si>
+  <si>
+    <t>0.0366,0.0051,0.9649,0.0039</t>
+  </si>
+  <si>
+    <t>0.1488,0.0177,0.8975,0.0073</t>
+  </si>
+  <si>
+    <t>0.4714,0.0065,0.7071,0.0011</t>
+  </si>
+  <si>
+    <t>0.3565,0.2433,0.4200,0.0189</t>
+  </si>
+  <si>
+    <t>0.5577,0.1466,0.2743,0.0094</t>
+  </si>
+  <si>
+    <t>0.2732,0.0198,0.7710,0.0076</t>
+  </si>
+  <si>
+    <t>0.8214,0.0521,0.0881,0.0200</t>
+  </si>
+  <si>
+    <t>0.3934,0.7033,0.0077,0.0015</t>
+  </si>
+  <si>
+    <t>0.2150,0.8502,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.6241,0.4965,0.0076,0.0008</t>
+  </si>
+  <si>
+    <t>0.9438,0.0877,0.0040,0.0017</t>
+  </si>
+  <si>
+    <t>0.9431,0.0600,0.0054,0.0037</t>
+  </si>
+  <si>
+    <t>0.4371,0.2050,0.4001,0.0160</t>
+  </si>
+  <si>
+    <t>0.9223,0.0121,0.0293,0.0085</t>
+  </si>
+  <si>
+    <t>0.7748,0.0243,0.0367,0.0975</t>
+  </si>
+  <si>
+    <t>0.5716,0.1096,0.3460,0.0585</t>
+  </si>
+  <si>
+    <t>0.6667,0.0146,0.3408,0.0149</t>
+  </si>
+  <si>
+    <t>0.0160,0.0018,0.9689,0.0212</t>
+  </si>
+  <si>
+    <t>0.0299,0.0270,0.9319,0.0213</t>
+  </si>
+  <si>
+    <t>0.0072,0.0793,0.9733,0.0043</t>
+  </si>
+  <si>
+    <t>0.0291,0.1562,0.9040,0.0019</t>
+  </si>
+  <si>
+    <t>0.0085,0.1023,0.9692,0.0013</t>
+  </si>
+  <si>
+    <t>0.9907,0.0043,0.0002,0.0009</t>
+  </si>
+  <si>
+    <t>0.9584,0.0336,0.0049,0.0048</t>
+  </si>
+  <si>
+    <t>0.9931,0.0031,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9888,0.0034,0.0020,0.0018</t>
+  </si>
+  <si>
+    <t>0.9628,0.0659,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9909,0.0063,0.0011,0.0007</t>
+  </si>
+  <si>
+    <t>0.9925,0.0035,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9854,0.0105,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.0615,0.0046,0.9394,0.0078</t>
+  </si>
+  <si>
+    <t>0.3135,0.4635,0.2913,0.0289</t>
+  </si>
+  <si>
+    <t>0.8540,0.0295,0.0907,0.0192</t>
+  </si>
+  <si>
+    <t>0.0030,0.0017,0.9963,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0064,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0406,0.0628,0.9336,0.0027</t>
+  </si>
+  <si>
+    <t>0.0013,0.0360,0.9949,0.0011</t>
+  </si>
+  <si>
+    <t>0.0286,0.0283,0.9527,0.0017</t>
+  </si>
+  <si>
+    <t>0.0027,0.0463,0.9878,0.0020</t>
+  </si>
+  <si>
+    <t>0.0058,0.0036,0.9765,0.0182</t>
+  </si>
+  <si>
+    <t>0.1754,0.0318,0.8223,0.0046</t>
+  </si>
+  <si>
+    <t>0.5134,0.0045,0.5459,0.0098</t>
+  </si>
+  <si>
+    <t>0.6856,0.0079,0.4137,0.0043</t>
+  </si>
+  <si>
+    <t>0.8649,0.0260,0.0305,0.0447</t>
+  </si>
+  <si>
+    <t>0.9881,0.0046,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9869,0.0047,0.0010,0.0027</t>
+  </si>
+  <si>
+    <t>0.9880,0.0078,0.0027,0.0012</t>
+  </si>
+  <si>
+    <t>0.9798,0.0166,0.0015,0.0014</t>
+  </si>
+  <si>
+    <t>0.9892,0.0040,0.0012,0.0016</t>
+  </si>
+  <si>
+    <t>0.9900,0.0043,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9863,0.0105,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9812,0.0205,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.0553,0.3251,0.6958,0.0084</t>
+  </si>
+  <si>
+    <t>0.0023,0.0877,0.9880,0.0004</t>
+  </si>
+  <si>
+    <t>0.0031,0.1121,0.9682,0.0047</t>
+  </si>
+  <si>
+    <t>0.1203,0.2003,0.5593,0.0014</t>
+  </si>
+  <si>
+    <t>0.0431,0.0107,0.9614,0.0027</t>
+  </si>
+  <si>
+    <t>0.1107,0.0062,0.5662,0.3242</t>
+  </si>
+  <si>
+    <t>0.0602,0.0053,0.9370,0.0115</t>
+  </si>
+  <si>
+    <t>0.0251,0.0076,0.9536,0.0191</t>
+  </si>
+  <si>
+    <t>0.4037,0.0009,0.0043,0.7456</t>
+  </si>
+  <si>
+    <t>0.0419,0.0304,0.0135,0.9676</t>
+  </si>
+  <si>
+    <t>0.0040,0.0101,0.0022,0.9961</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0024,0.9977</t>
+  </si>
+  <si>
+    <t>0.0021,0.0002,0.0001,0.9992</t>
+  </si>
+  <si>
+    <t>0.8392,0.0755,0.0383,0.0380</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1987,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2130,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,10 +2155,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2270,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2281,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,10 +2365,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,7 +2578,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2816,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2925,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2942,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,10 +2953,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3124,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3152,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3163,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3541,7 +3544,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3555,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3597,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3670,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3712,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,10 +3849,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3922,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4006,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4090,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4199,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4384,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,10 +4451,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4538,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4594,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,10 +4619,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,7 +4636,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4689,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4720,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4731,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4773,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5168,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5179,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5406,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5448,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5518,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
